--- a/new original/_Dialog/Drama/_chara.xlsx
+++ b/new original/_Dialog/Drama/_chara.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="112">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -263,6 +263,42 @@
   </si>
   <si>
     <t xml:space="preserve">(#self is too pumped up at the party.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#selfはあなた達二人に乾杯した！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self raises a toast to the two of you!)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_love</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#selfは幸せそうにあなたに微笑んだ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(#self smiles at you happily.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_hater</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(プンスコ！)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Pouting in a huff.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">wedding_cutter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">…あなた（ポッ）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...My love. (blushing)</t>
   </si>
   <si>
     <t xml:space="preserve">encounter_mob</t>
@@ -631,7 +667,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L134"/>
+  <dimension ref="A1:L146"/>
   <sheetFormatPr defaultColWidth="9.0546875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="21.14"/>
@@ -682,7 +718,7 @@
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="H2" s="1" t="n">
         <f aca="false">MAX(H4:H1048576)</f>
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1223,148 +1259,232 @@
         <v>25</v>
       </c>
     </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
     <row r="108" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
-        <v>81</v>
+      <c r="H108" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="I108" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="J108" s="4" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H109" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="I109" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>83</v>
+      <c r="B109" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J110" s="4"/>
+      <c r="A110" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>31</v>
-      </c>
       <c r="H111" s="1" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I111" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="J111" s="1" t="s">
+      <c r="J111" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="D112" s="1" t="s">
+    </row>
+    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H114" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="I114" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="J114" s="4" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H117" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="I117" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="J117" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H121" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J121" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J122" s="4"/>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H112" s="1" t="n">
+      <c r="H123" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="J123" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D124" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H124" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="I112" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="J112" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J113" s="4"/>
-    </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J114" s="4"/>
-    </row>
-    <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="J115" s="4"/>
-    </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D119" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B120" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H123" s="1" t="n">
+      <c r="I124" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J124" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J125" s="4"/>
+    </row>
+    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J126" s="4"/>
+    </row>
+    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J127" s="4"/>
+    </row>
+    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D131" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B132" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H135" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="I123" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="J123" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D124" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B126" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H129" s="1" t="n">
+      <c r="I135" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="J135" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D136" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B138" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H141" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="I129" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J129" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B130" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H133" s="1" t="n">
+      <c r="I141" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="J141" s="4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B142" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H145" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="I133" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="J133" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B134" s="1" t="s">
+      <c r="I145" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="J145" s="4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B146" s="1" t="s">
         <v>25</v>
       </c>
     </row>
